--- a/idecba/industria_ing.xlsx
+++ b/idecba/industria_ing.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20745" windowHeight="4590"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25455" windowHeight="8745"/>
   </bookViews>
   <sheets>
     <sheet name="ee_industria_ingresos_fabriles" sheetId="2" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="63">
   <si>
     <t xml:space="preserve">Alimentos, bebidas y tabaco </t>
   </si>
@@ -224,7 +224,10 @@
     <t>2025*</t>
   </si>
   <si>
-    <t>Ingresos fabriles por rama de actividad en valores corrientes y constantes (Índice base octubre 2001 = 100). Ciudad de Buenos Aires. Octubre 2001/Diciembre 2025</t>
+    <t>Ingresos fabriles por rama de actividad en valores corrientes y constantes (Índice base octubre 2001 = 100). Ciudad de Buenos Aires. Octubre 2001/Marzo 2026</t>
+  </si>
+  <si>
+    <t>2026*</t>
   </si>
 </sst>
 </file>
@@ -1446,10 +1449,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1460,6 +1469,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="3" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="3" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="3" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1479,12 +1500,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1492,18 +1507,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="3" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="3" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="3" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="43" xfId="35" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1863,7 +1866,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Hoja2"/>
-  <dimension ref="A1:V472"/>
+  <dimension ref="A1:V475"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="15" customWidth="1"/>
@@ -1874,20 +1877,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="92" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="92"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="92"/>
+      <c r="K1" s="92"/>
+      <c r="L1" s="92"/>
       <c r="M1" s="5"/>
       <c r="N1" s="5"/>
       <c r="O1" s="4"/>
@@ -1900,40 +1903,40 @@
       <c r="V1" s="4"/>
     </row>
     <row r="2" spans="1:22" s="4" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="93" t="s">
+      <c r="A2" s="99" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="94" t="s">
+      <c r="B2" s="100" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="102" t="s">
+      <c r="C2" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
-      <c r="H2" s="103"/>
-      <c r="I2" s="103"/>
-      <c r="J2" s="103"/>
-      <c r="K2" s="103"/>
-      <c r="L2" s="104"/>
-      <c r="M2" s="90" t="s">
+      <c r="D2" s="94"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
+      <c r="H2" s="94"/>
+      <c r="I2" s="94"/>
+      <c r="J2" s="94"/>
+      <c r="K2" s="94"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="91"/>
-      <c r="O2" s="91"/>
-      <c r="P2" s="91"/>
-      <c r="Q2" s="91"/>
-      <c r="R2" s="91"/>
-      <c r="S2" s="91"/>
-      <c r="T2" s="91"/>
-      <c r="U2" s="91"/>
-      <c r="V2" s="92"/>
+      <c r="N2" s="97"/>
+      <c r="O2" s="97"/>
+      <c r="P2" s="97"/>
+      <c r="Q2" s="97"/>
+      <c r="R2" s="97"/>
+      <c r="S2" s="97"/>
+      <c r="T2" s="97"/>
+      <c r="U2" s="97"/>
+      <c r="V2" s="98"/>
     </row>
     <row r="3" spans="1:22" ht="66" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="89"/>
-      <c r="B3" s="95"/>
+      <c r="A3" s="91"/>
+      <c r="B3" s="101"/>
       <c r="C3" s="6" t="s">
         <v>8</v>
       </c>
@@ -1996,7 +1999,7 @@
       </c>
     </row>
     <row r="4" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="87">
+      <c r="A4" s="89">
         <v>2001</v>
       </c>
       <c r="B4" s="16" t="s">
@@ -2064,7 +2067,7 @@
       </c>
     </row>
     <row r="5" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="88"/>
+      <c r="A5" s="90"/>
       <c r="B5" s="17" t="s">
         <v>14</v>
       </c>
@@ -2130,7 +2133,7 @@
       </c>
     </row>
     <row r="6" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="89"/>
+      <c r="A6" s="91"/>
       <c r="B6" s="18" t="s">
         <v>15</v>
       </c>
@@ -2196,7 +2199,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="88">
+      <c r="A7" s="90">
         <v>2002</v>
       </c>
       <c r="B7" s="17" t="s">
@@ -2264,7 +2267,7 @@
       </c>
     </row>
     <row r="8" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="88"/>
+      <c r="A8" s="90"/>
       <c r="B8" s="17" t="s">
         <v>17</v>
       </c>
@@ -2330,7 +2333,7 @@
       </c>
     </row>
     <row r="9" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="88"/>
+      <c r="A9" s="90"/>
       <c r="B9" s="17" t="s">
         <v>18</v>
       </c>
@@ -2396,7 +2399,7 @@
       </c>
     </row>
     <row r="10" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="88"/>
+      <c r="A10" s="90"/>
       <c r="B10" s="17" t="s">
         <v>19</v>
       </c>
@@ -2462,7 +2465,7 @@
       </c>
     </row>
     <row r="11" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="88"/>
+      <c r="A11" s="90"/>
       <c r="B11" s="17" t="s">
         <v>20</v>
       </c>
@@ -2528,7 +2531,7 @@
       </c>
     </row>
     <row r="12" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="88"/>
+      <c r="A12" s="90"/>
       <c r="B12" s="17" t="s">
         <v>21</v>
       </c>
@@ -2594,7 +2597,7 @@
       </c>
     </row>
     <row r="13" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="88"/>
+      <c r="A13" s="90"/>
       <c r="B13" s="17" t="s">
         <v>22</v>
       </c>
@@ -2660,7 +2663,7 @@
       </c>
     </row>
     <row r="14" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="88"/>
+      <c r="A14" s="90"/>
       <c r="B14" s="17" t="s">
         <v>23</v>
       </c>
@@ -2726,7 +2729,7 @@
       </c>
     </row>
     <row r="15" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="88"/>
+      <c r="A15" s="90"/>
       <c r="B15" s="17" t="s">
         <v>24</v>
       </c>
@@ -2792,7 +2795,7 @@
       </c>
     </row>
     <row r="16" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="88"/>
+      <c r="A16" s="90"/>
       <c r="B16" s="17" t="s">
         <v>13</v>
       </c>
@@ -2858,7 +2861,7 @@
       </c>
     </row>
     <row r="17" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="88"/>
+      <c r="A17" s="90"/>
       <c r="B17" s="17" t="s">
         <v>14</v>
       </c>
@@ -2924,7 +2927,7 @@
       </c>
     </row>
     <row r="18" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="89"/>
+      <c r="A18" s="91"/>
       <c r="B18" s="18" t="s">
         <v>15</v>
       </c>
@@ -2990,7 +2993,7 @@
       </c>
     </row>
     <row r="19" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="88">
+      <c r="A19" s="90">
         <v>2003</v>
       </c>
       <c r="B19" s="17" t="s">
@@ -3058,7 +3061,7 @@
       </c>
     </row>
     <row r="20" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="88"/>
+      <c r="A20" s="90"/>
       <c r="B20" s="17" t="s">
         <v>17</v>
       </c>
@@ -3124,7 +3127,7 @@
       </c>
     </row>
     <row r="21" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="88"/>
+      <c r="A21" s="90"/>
       <c r="B21" s="17" t="s">
         <v>18</v>
       </c>
@@ -3190,7 +3193,7 @@
       </c>
     </row>
     <row r="22" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="88"/>
+      <c r="A22" s="90"/>
       <c r="B22" s="17" t="s">
         <v>19</v>
       </c>
@@ -3256,7 +3259,7 @@
       </c>
     </row>
     <row r="23" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="88"/>
+      <c r="A23" s="90"/>
       <c r="B23" s="17" t="s">
         <v>20</v>
       </c>
@@ -3322,7 +3325,7 @@
       </c>
     </row>
     <row r="24" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="88"/>
+      <c r="A24" s="90"/>
       <c r="B24" s="17" t="s">
         <v>21</v>
       </c>
@@ -3388,7 +3391,7 @@
       </c>
     </row>
     <row r="25" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="88"/>
+      <c r="A25" s="90"/>
       <c r="B25" s="17" t="s">
         <v>22</v>
       </c>
@@ -3454,7 +3457,7 @@
       </c>
     </row>
     <row r="26" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="88"/>
+      <c r="A26" s="90"/>
       <c r="B26" s="17" t="s">
         <v>23</v>
       </c>
@@ -3520,7 +3523,7 @@
       </c>
     </row>
     <row r="27" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="88"/>
+      <c r="A27" s="90"/>
       <c r="B27" s="17" t="s">
         <v>24</v>
       </c>
@@ -3586,7 +3589,7 @@
       </c>
     </row>
     <row r="28" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="88"/>
+      <c r="A28" s="90"/>
       <c r="B28" s="17" t="s">
         <v>13</v>
       </c>
@@ -3652,7 +3655,7 @@
       </c>
     </row>
     <row r="29" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="88"/>
+      <c r="A29" s="90"/>
       <c r="B29" s="17" t="s">
         <v>14</v>
       </c>
@@ -3718,7 +3721,7 @@
       </c>
     </row>
     <row r="30" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="89"/>
+      <c r="A30" s="91"/>
       <c r="B30" s="18" t="s">
         <v>15</v>
       </c>
@@ -3784,7 +3787,7 @@
       </c>
     </row>
     <row r="31" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="88">
+      <c r="A31" s="90">
         <v>2004</v>
       </c>
       <c r="B31" s="17" t="s">
@@ -3852,7 +3855,7 @@
       </c>
     </row>
     <row r="32" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="88"/>
+      <c r="A32" s="90"/>
       <c r="B32" s="17" t="s">
         <v>17</v>
       </c>
@@ -3918,7 +3921,7 @@
       </c>
     </row>
     <row r="33" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="88"/>
+      <c r="A33" s="90"/>
       <c r="B33" s="17" t="s">
         <v>18</v>
       </c>
@@ -3984,7 +3987,7 @@
       </c>
     </row>
     <row r="34" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="88"/>
+      <c r="A34" s="90"/>
       <c r="B34" s="17" t="s">
         <v>19</v>
       </c>
@@ -4050,7 +4053,7 @@
       </c>
     </row>
     <row r="35" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="88"/>
+      <c r="A35" s="90"/>
       <c r="B35" s="17" t="s">
         <v>20</v>
       </c>
@@ -4116,7 +4119,7 @@
       </c>
     </row>
     <row r="36" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="88"/>
+      <c r="A36" s="90"/>
       <c r="B36" s="17" t="s">
         <v>21</v>
       </c>
@@ -4182,7 +4185,7 @@
       </c>
     </row>
     <row r="37" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="88"/>
+      <c r="A37" s="90"/>
       <c r="B37" s="17" t="s">
         <v>22</v>
       </c>
@@ -4248,7 +4251,7 @@
       </c>
     </row>
     <row r="38" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="88"/>
+      <c r="A38" s="90"/>
       <c r="B38" s="17" t="s">
         <v>23</v>
       </c>
@@ -4314,7 +4317,7 @@
       </c>
     </row>
     <row r="39" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="88"/>
+      <c r="A39" s="90"/>
       <c r="B39" s="17" t="s">
         <v>24</v>
       </c>
@@ -4380,7 +4383,7 @@
       </c>
     </row>
     <row r="40" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="88"/>
+      <c r="A40" s="90"/>
       <c r="B40" s="17" t="s">
         <v>13</v>
       </c>
@@ -4446,7 +4449,7 @@
       </c>
     </row>
     <row r="41" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="88"/>
+      <c r="A41" s="90"/>
       <c r="B41" s="17" t="s">
         <v>14</v>
       </c>
@@ -4512,7 +4515,7 @@
       </c>
     </row>
     <row r="42" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="89"/>
+      <c r="A42" s="91"/>
       <c r="B42" s="18" t="s">
         <v>15</v>
       </c>
@@ -4578,7 +4581,7 @@
       </c>
     </row>
     <row r="43" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="88">
+      <c r="A43" s="90">
         <v>2005</v>
       </c>
       <c r="B43" s="17" t="s">
@@ -4646,7 +4649,7 @@
       </c>
     </row>
     <row r="44" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="88"/>
+      <c r="A44" s="90"/>
       <c r="B44" s="17" t="s">
         <v>17</v>
       </c>
@@ -4712,7 +4715,7 @@
       </c>
     </row>
     <row r="45" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="88"/>
+      <c r="A45" s="90"/>
       <c r="B45" s="17" t="s">
         <v>18</v>
       </c>
@@ -4778,7 +4781,7 @@
       </c>
     </row>
     <row r="46" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="88"/>
+      <c r="A46" s="90"/>
       <c r="B46" s="17" t="s">
         <v>19</v>
       </c>
@@ -4844,7 +4847,7 @@
       </c>
     </row>
     <row r="47" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="88"/>
+      <c r="A47" s="90"/>
       <c r="B47" s="17" t="s">
         <v>20</v>
       </c>
@@ -4910,7 +4913,7 @@
       </c>
     </row>
     <row r="48" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="88"/>
+      <c r="A48" s="90"/>
       <c r="B48" s="17" t="s">
         <v>21</v>
       </c>
@@ -4976,7 +4979,7 @@
       </c>
     </row>
     <row r="49" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="88"/>
+      <c r="A49" s="90"/>
       <c r="B49" s="17" t="s">
         <v>22</v>
       </c>
@@ -5042,7 +5045,7 @@
       </c>
     </row>
     <row r="50" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="88"/>
+      <c r="A50" s="90"/>
       <c r="B50" s="17" t="s">
         <v>23</v>
       </c>
@@ -5108,7 +5111,7 @@
       </c>
     </row>
     <row r="51" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="88"/>
+      <c r="A51" s="90"/>
       <c r="B51" s="17" t="s">
         <v>24</v>
       </c>
@@ -5174,7 +5177,7 @@
       </c>
     </row>
     <row r="52" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="88"/>
+      <c r="A52" s="90"/>
       <c r="B52" s="17" t="s">
         <v>13</v>
       </c>
@@ -5240,7 +5243,7 @@
       </c>
     </row>
     <row r="53" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="88"/>
+      <c r="A53" s="90"/>
       <c r="B53" s="17" t="s">
         <v>14</v>
       </c>
@@ -5306,7 +5309,7 @@
       </c>
     </row>
     <row r="54" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="89"/>
+      <c r="A54" s="91"/>
       <c r="B54" s="18" t="s">
         <v>15</v>
       </c>
@@ -5372,7 +5375,7 @@
       </c>
     </row>
     <row r="55" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="88">
+      <c r="A55" s="90">
         <v>2006</v>
       </c>
       <c r="B55" s="17" t="s">
@@ -5440,7 +5443,7 @@
       </c>
     </row>
     <row r="56" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="88"/>
+      <c r="A56" s="90"/>
       <c r="B56" s="17" t="s">
         <v>17</v>
       </c>
@@ -5506,7 +5509,7 @@
       </c>
     </row>
     <row r="57" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="88"/>
+      <c r="A57" s="90"/>
       <c r="B57" s="17" t="s">
         <v>18</v>
       </c>
@@ -5572,7 +5575,7 @@
       </c>
     </row>
     <row r="58" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="88"/>
+      <c r="A58" s="90"/>
       <c r="B58" s="17" t="s">
         <v>19</v>
       </c>
@@ -5638,7 +5641,7 @@
       </c>
     </row>
     <row r="59" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="88"/>
+      <c r="A59" s="90"/>
       <c r="B59" s="17" t="s">
         <v>20</v>
       </c>
@@ -5704,7 +5707,7 @@
       </c>
     </row>
     <row r="60" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="88"/>
+      <c r="A60" s="90"/>
       <c r="B60" s="17" t="s">
         <v>21</v>
       </c>
@@ -5770,7 +5773,7 @@
       </c>
     </row>
     <row r="61" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="88"/>
+      <c r="A61" s="90"/>
       <c r="B61" s="17" t="s">
         <v>22</v>
       </c>
@@ -5836,7 +5839,7 @@
       </c>
     </row>
     <row r="62" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="88"/>
+      <c r="A62" s="90"/>
       <c r="B62" s="17" t="s">
         <v>23</v>
       </c>
@@ -5902,7 +5905,7 @@
       </c>
     </row>
     <row r="63" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="88"/>
+      <c r="A63" s="90"/>
       <c r="B63" s="17" t="s">
         <v>24</v>
       </c>
@@ -5968,7 +5971,7 @@
       </c>
     </row>
     <row r="64" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="88"/>
+      <c r="A64" s="90"/>
       <c r="B64" s="17" t="s">
         <v>13</v>
       </c>
@@ -6034,7 +6037,7 @@
       </c>
     </row>
     <row r="65" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="88"/>
+      <c r="A65" s="90"/>
       <c r="B65" s="17" t="s">
         <v>14</v>
       </c>
@@ -6100,7 +6103,7 @@
       </c>
     </row>
     <row r="66" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="89"/>
+      <c r="A66" s="91"/>
       <c r="B66" s="18" t="s">
         <v>15</v>
       </c>
@@ -6166,7 +6169,7 @@
       </c>
     </row>
     <row r="67" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="88">
+      <c r="A67" s="90">
         <v>2007</v>
       </c>
       <c r="B67" s="17" t="s">
@@ -6234,7 +6237,7 @@
       </c>
     </row>
     <row r="68" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="88"/>
+      <c r="A68" s="90"/>
       <c r="B68" s="17" t="s">
         <v>17</v>
       </c>
@@ -6300,7 +6303,7 @@
       </c>
     </row>
     <row r="69" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="88"/>
+      <c r="A69" s="90"/>
       <c r="B69" s="17" t="s">
         <v>18</v>
       </c>
@@ -6366,7 +6369,7 @@
       </c>
     </row>
     <row r="70" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="88"/>
+      <c r="A70" s="90"/>
       <c r="B70" s="17" t="s">
         <v>19</v>
       </c>
@@ -6432,7 +6435,7 @@
       </c>
     </row>
     <row r="71" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="88"/>
+      <c r="A71" s="90"/>
       <c r="B71" s="17" t="s">
         <v>20</v>
       </c>
@@ -6498,7 +6501,7 @@
       </c>
     </row>
     <row r="72" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="88"/>
+      <c r="A72" s="90"/>
       <c r="B72" s="17" t="s">
         <v>21</v>
       </c>
@@ -6564,7 +6567,7 @@
       </c>
     </row>
     <row r="73" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="88"/>
+      <c r="A73" s="90"/>
       <c r="B73" s="17" t="s">
         <v>22</v>
       </c>
@@ -6630,7 +6633,7 @@
       </c>
     </row>
     <row r="74" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="88"/>
+      <c r="A74" s="90"/>
       <c r="B74" s="17" t="s">
         <v>23</v>
       </c>
@@ -6696,7 +6699,7 @@
       </c>
     </row>
     <row r="75" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="88"/>
+      <c r="A75" s="90"/>
       <c r="B75" s="17" t="s">
         <v>24</v>
       </c>
@@ -6762,7 +6765,7 @@
       </c>
     </row>
     <row r="76" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="88"/>
+      <c r="A76" s="90"/>
       <c r="B76" s="17" t="s">
         <v>13</v>
       </c>
@@ -6828,7 +6831,7 @@
       </c>
     </row>
     <row r="77" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="88"/>
+      <c r="A77" s="90"/>
       <c r="B77" s="17" t="s">
         <v>14</v>
       </c>
@@ -6894,7 +6897,7 @@
       </c>
     </row>
     <row r="78" spans="1:22" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="89"/>
+      <c r="A78" s="91"/>
       <c r="B78" s="18" t="s">
         <v>15</v>
       </c>
@@ -6960,7 +6963,7 @@
       </c>
     </row>
     <row r="79" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A79" s="88">
+      <c r="A79" s="90">
         <v>2008</v>
       </c>
       <c r="B79" s="17" t="s">
@@ -7028,7 +7031,7 @@
       </c>
     </row>
     <row r="80" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A80" s="88"/>
+      <c r="A80" s="90"/>
       <c r="B80" s="17" t="s">
         <v>17</v>
       </c>
@@ -7094,7 +7097,7 @@
       </c>
     </row>
     <row r="81" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A81" s="88"/>
+      <c r="A81" s="90"/>
       <c r="B81" s="17" t="s">
         <v>18</v>
       </c>
@@ -7160,7 +7163,7 @@
       </c>
     </row>
     <row r="82" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A82" s="88"/>
+      <c r="A82" s="90"/>
       <c r="B82" s="17" t="s">
         <v>19</v>
       </c>
@@ -7226,7 +7229,7 @@
       </c>
     </row>
     <row r="83" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A83" s="88"/>
+      <c r="A83" s="90"/>
       <c r="B83" s="17" t="s">
         <v>20</v>
       </c>
@@ -7292,7 +7295,7 @@
       </c>
     </row>
     <row r="84" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A84" s="88"/>
+      <c r="A84" s="90"/>
       <c r="B84" s="17" t="s">
         <v>21</v>
       </c>
@@ -7358,7 +7361,7 @@
       </c>
     </row>
     <row r="85" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A85" s="88"/>
+      <c r="A85" s="90"/>
       <c r="B85" s="17" t="s">
         <v>22</v>
       </c>
@@ -7424,7 +7427,7 @@
       </c>
     </row>
     <row r="86" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A86" s="88"/>
+      <c r="A86" s="90"/>
       <c r="B86" s="17" t="s">
         <v>23</v>
       </c>
@@ -7490,7 +7493,7 @@
       </c>
     </row>
     <row r="87" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A87" s="88"/>
+      <c r="A87" s="90"/>
       <c r="B87" s="17" t="s">
         <v>24</v>
       </c>
@@ -7556,7 +7559,7 @@
       </c>
     </row>
     <row r="88" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A88" s="88"/>
+      <c r="A88" s="90"/>
       <c r="B88" s="17" t="s">
         <v>13</v>
       </c>
@@ -7622,7 +7625,7 @@
       </c>
     </row>
     <row r="89" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A89" s="88"/>
+      <c r="A89" s="90"/>
       <c r="B89" s="17" t="s">
         <v>14</v>
       </c>
@@ -7688,7 +7691,7 @@
       </c>
     </row>
     <row r="90" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A90" s="89"/>
+      <c r="A90" s="91"/>
       <c r="B90" s="18" t="s">
         <v>15</v>
       </c>
@@ -7754,7 +7757,7 @@
       </c>
     </row>
     <row r="91" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A91" s="87">
+      <c r="A91" s="89">
         <v>2009</v>
       </c>
       <c r="B91" s="17" t="s">
@@ -7822,7 +7825,7 @@
       </c>
     </row>
     <row r="92" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A92" s="88"/>
+      <c r="A92" s="90"/>
       <c r="B92" s="17" t="s">
         <v>17</v>
       </c>
@@ -7888,7 +7891,7 @@
       </c>
     </row>
     <row r="93" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A93" s="88"/>
+      <c r="A93" s="90"/>
       <c r="B93" s="17" t="s">
         <v>18</v>
       </c>
@@ -7954,7 +7957,7 @@
       </c>
     </row>
     <row r="94" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A94" s="88"/>
+      <c r="A94" s="90"/>
       <c r="B94" s="17" t="s">
         <v>19</v>
       </c>
@@ -8020,7 +8023,7 @@
       </c>
     </row>
     <row r="95" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A95" s="88"/>
+      <c r="A95" s="90"/>
       <c r="B95" s="17" t="s">
         <v>20</v>
       </c>
@@ -8086,7 +8089,7 @@
       </c>
     </row>
     <row r="96" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A96" s="88"/>
+      <c r="A96" s="90"/>
       <c r="B96" s="17" t="s">
         <v>21</v>
       </c>
@@ -8152,7 +8155,7 @@
       </c>
     </row>
     <row r="97" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A97" s="88"/>
+      <c r="A97" s="90"/>
       <c r="B97" s="17" t="s">
         <v>22</v>
       </c>
@@ -8218,7 +8221,7 @@
       </c>
     </row>
     <row r="98" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A98" s="88"/>
+      <c r="A98" s="90"/>
       <c r="B98" s="17" t="s">
         <v>23</v>
       </c>
@@ -8284,7 +8287,7 @@
       </c>
     </row>
     <row r="99" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A99" s="88"/>
+      <c r="A99" s="90"/>
       <c r="B99" s="17" t="s">
         <v>24</v>
       </c>
@@ -8350,7 +8353,7 @@
       </c>
     </row>
     <row r="100" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A100" s="88"/>
+      <c r="A100" s="90"/>
       <c r="B100" s="17" t="s">
         <v>13</v>
       </c>
@@ -8416,7 +8419,7 @@
       </c>
     </row>
     <row r="101" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A101" s="88"/>
+      <c r="A101" s="90"/>
       <c r="B101" s="17" t="s">
         <v>14</v>
       </c>
@@ -8482,7 +8485,7 @@
       </c>
     </row>
     <row r="102" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A102" s="89"/>
+      <c r="A102" s="91"/>
       <c r="B102" s="18" t="s">
         <v>15</v>
       </c>
@@ -8548,7 +8551,7 @@
       </c>
     </row>
     <row r="103" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A103" s="87">
+      <c r="A103" s="89">
         <v>2010</v>
       </c>
       <c r="B103" s="17" t="s">
@@ -8616,7 +8619,7 @@
       </c>
     </row>
     <row r="104" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A104" s="88"/>
+      <c r="A104" s="90"/>
       <c r="B104" s="17" t="s">
         <v>17</v>
       </c>
@@ -8682,7 +8685,7 @@
       </c>
     </row>
     <row r="105" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A105" s="88"/>
+      <c r="A105" s="90"/>
       <c r="B105" s="17" t="s">
         <v>18</v>
       </c>
@@ -8748,7 +8751,7 @@
       </c>
     </row>
     <row r="106" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A106" s="88"/>
+      <c r="A106" s="90"/>
       <c r="B106" s="17" t="s">
         <v>19</v>
       </c>
@@ -8814,7 +8817,7 @@
       </c>
     </row>
     <row r="107" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A107" s="88"/>
+      <c r="A107" s="90"/>
       <c r="B107" s="17" t="s">
         <v>20</v>
       </c>
@@ -8880,7 +8883,7 @@
       </c>
     </row>
     <row r="108" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A108" s="88"/>
+      <c r="A108" s="90"/>
       <c r="B108" s="17" t="s">
         <v>21</v>
       </c>
@@ -8946,7 +8949,7 @@
       </c>
     </row>
     <row r="109" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A109" s="88"/>
+      <c r="A109" s="90"/>
       <c r="B109" s="17" t="s">
         <v>22</v>
       </c>
@@ -9012,7 +9015,7 @@
       </c>
     </row>
     <row r="110" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A110" s="88"/>
+      <c r="A110" s="90"/>
       <c r="B110" s="17" t="s">
         <v>23</v>
       </c>
@@ -9078,7 +9081,7 @@
       </c>
     </row>
     <row r="111" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A111" s="88"/>
+      <c r="A111" s="90"/>
       <c r="B111" s="17" t="s">
         <v>24</v>
       </c>
@@ -9144,7 +9147,7 @@
       </c>
     </row>
     <row r="112" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A112" s="88"/>
+      <c r="A112" s="90"/>
       <c r="B112" s="17" t="s">
         <v>13</v>
       </c>
@@ -9210,7 +9213,7 @@
       </c>
     </row>
     <row r="113" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A113" s="88"/>
+      <c r="A113" s="90"/>
       <c r="B113" s="17" t="s">
         <v>14</v>
       </c>
@@ -9276,7 +9279,7 @@
       </c>
     </row>
     <row r="114" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A114" s="89"/>
+      <c r="A114" s="91"/>
       <c r="B114" s="18" t="s">
         <v>15</v>
       </c>
@@ -9342,7 +9345,7 @@
       </c>
     </row>
     <row r="115" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A115" s="87">
+      <c r="A115" s="89">
         <v>2011</v>
       </c>
       <c r="B115" s="17" t="s">
@@ -9410,7 +9413,7 @@
       </c>
     </row>
     <row r="116" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A116" s="88"/>
+      <c r="A116" s="90"/>
       <c r="B116" s="17" t="s">
         <v>17</v>
       </c>
@@ -9476,7 +9479,7 @@
       </c>
     </row>
     <row r="117" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A117" s="88"/>
+      <c r="A117" s="90"/>
       <c r="B117" s="17" t="s">
         <v>18</v>
       </c>
@@ -9542,7 +9545,7 @@
       </c>
     </row>
     <row r="118" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A118" s="88"/>
+      <c r="A118" s="90"/>
       <c r="B118" s="17" t="s">
         <v>19</v>
       </c>
@@ -9608,7 +9611,7 @@
       </c>
     </row>
     <row r="119" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A119" s="88"/>
+      <c r="A119" s="90"/>
       <c r="B119" s="17" t="s">
         <v>20</v>
       </c>
@@ -9674,7 +9677,7 @@
       </c>
     </row>
     <row r="120" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A120" s="88"/>
+      <c r="A120" s="90"/>
       <c r="B120" s="17" t="s">
         <v>21</v>
       </c>
@@ -9740,7 +9743,7 @@
       </c>
     </row>
     <row r="121" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A121" s="88"/>
+      <c r="A121" s="90"/>
       <c r="B121" s="17" t="s">
         <v>22</v>
       </c>
@@ -9806,7 +9809,7 @@
       </c>
     </row>
     <row r="122" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A122" s="88"/>
+      <c r="A122" s="90"/>
       <c r="B122" s="17" t="s">
         <v>23</v>
       </c>
@@ -9872,7 +9875,7 @@
       </c>
     </row>
     <row r="123" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A123" s="88"/>
+      <c r="A123" s="90"/>
       <c r="B123" s="17" t="s">
         <v>24</v>
       </c>
@@ -9938,7 +9941,7 @@
       </c>
     </row>
     <row r="124" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A124" s="88"/>
+      <c r="A124" s="90"/>
       <c r="B124" s="17" t="s">
         <v>13</v>
       </c>
@@ -10004,7 +10007,7 @@
       </c>
     </row>
     <row r="125" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A125" s="88"/>
+      <c r="A125" s="90"/>
       <c r="B125" s="17" t="s">
         <v>14</v>
       </c>
@@ -10070,7 +10073,7 @@
       </c>
     </row>
     <row r="126" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A126" s="89"/>
+      <c r="A126" s="91"/>
       <c r="B126" s="18" t="s">
         <v>15</v>
       </c>
@@ -10136,7 +10139,7 @@
       </c>
     </row>
     <row r="127" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A127" s="87">
+      <c r="A127" s="89">
         <v>2012</v>
       </c>
       <c r="B127" s="17" t="s">
@@ -10204,7 +10207,7 @@
       </c>
     </row>
     <row r="128" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A128" s="88"/>
+      <c r="A128" s="90"/>
       <c r="B128" s="17" t="s">
         <v>17</v>
       </c>
@@ -10270,7 +10273,7 @@
       </c>
     </row>
     <row r="129" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A129" s="88"/>
+      <c r="A129" s="90"/>
       <c r="B129" s="17" t="s">
         <v>18</v>
       </c>
@@ -10336,7 +10339,7 @@
       </c>
     </row>
     <row r="130" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A130" s="88"/>
+      <c r="A130" s="90"/>
       <c r="B130" s="17" t="s">
         <v>19</v>
       </c>
@@ -10402,7 +10405,7 @@
       </c>
     </row>
     <row r="131" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A131" s="88"/>
+      <c r="A131" s="90"/>
       <c r="B131" s="17" t="s">
         <v>20</v>
       </c>
@@ -10468,7 +10471,7 @@
       </c>
     </row>
     <row r="132" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A132" s="88"/>
+      <c r="A132" s="90"/>
       <c r="B132" s="17" t="s">
         <v>21</v>
       </c>
@@ -10534,7 +10537,7 @@
       </c>
     </row>
     <row r="133" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A133" s="88"/>
+      <c r="A133" s="90"/>
       <c r="B133" s="17" t="s">
         <v>22</v>
       </c>
@@ -10600,7 +10603,7 @@
       </c>
     </row>
     <row r="134" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A134" s="88"/>
+      <c r="A134" s="90"/>
       <c r="B134" s="17" t="s">
         <v>23</v>
       </c>
@@ -10666,7 +10669,7 @@
       </c>
     </row>
     <row r="135" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A135" s="88"/>
+      <c r="A135" s="90"/>
       <c r="B135" s="17" t="s">
         <v>24</v>
       </c>
@@ -10732,7 +10735,7 @@
       </c>
     </row>
     <row r="136" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A136" s="88"/>
+      <c r="A136" s="90"/>
       <c r="B136" s="17" t="s">
         <v>13</v>
       </c>
@@ -10798,7 +10801,7 @@
       </c>
     </row>
     <row r="137" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A137" s="88"/>
+      <c r="A137" s="90"/>
       <c r="B137" s="17" t="s">
         <v>14</v>
       </c>
@@ -10864,7 +10867,7 @@
       </c>
     </row>
     <row r="138" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A138" s="89"/>
+      <c r="A138" s="91"/>
       <c r="B138" s="18" t="s">
         <v>15</v>
       </c>
@@ -10930,7 +10933,7 @@
       </c>
     </row>
     <row r="139" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A139" s="87">
+      <c r="A139" s="89">
         <v>2013</v>
       </c>
       <c r="B139" s="16" t="s">
@@ -10998,7 +11001,7 @@
       </c>
     </row>
     <row r="140" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A140" s="88"/>
+      <c r="A140" s="90"/>
       <c r="B140" s="17" t="s">
         <v>17</v>
       </c>
@@ -11064,7 +11067,7 @@
       </c>
     </row>
     <row r="141" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="88"/>
+      <c r="A141" s="90"/>
       <c r="B141" s="17" t="s">
         <v>18</v>
       </c>
@@ -11130,7 +11133,7 @@
       </c>
     </row>
     <row r="142" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A142" s="88"/>
+      <c r="A142" s="90"/>
       <c r="B142" s="17" t="s">
         <v>19</v>
       </c>
@@ -11196,7 +11199,7 @@
       </c>
     </row>
     <row r="143" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A143" s="88"/>
+      <c r="A143" s="90"/>
       <c r="B143" s="17" t="s">
         <v>20</v>
       </c>
@@ -11262,7 +11265,7 @@
       </c>
     </row>
     <row r="144" spans="1:22" s="12" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="88"/>
+      <c r="A144" s="90"/>
       <c r="B144" s="43" t="s">
         <v>21</v>
       </c>
@@ -11328,7 +11331,7 @@
       </c>
     </row>
     <row r="145" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A145" s="88"/>
+      <c r="A145" s="90"/>
       <c r="B145" s="17" t="s">
         <v>22</v>
       </c>
@@ -11394,7 +11397,7 @@
       </c>
     </row>
     <row r="146" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="88"/>
+      <c r="A146" s="90"/>
       <c r="B146" s="43" t="s">
         <v>23</v>
       </c>
@@ -11460,7 +11463,7 @@
       </c>
     </row>
     <row r="147" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A147" s="88"/>
+      <c r="A147" s="90"/>
       <c r="B147" s="44" t="s">
         <v>26</v>
       </c>
@@ -11526,7 +11529,7 @@
       </c>
     </row>
     <row r="148" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A148" s="88"/>
+      <c r="A148" s="90"/>
       <c r="B148" s="44" t="s">
         <v>13</v>
       </c>
@@ -11592,7 +11595,7 @@
       </c>
     </row>
     <row r="149" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A149" s="88"/>
+      <c r="A149" s="90"/>
       <c r="B149" s="44" t="s">
         <v>14</v>
       </c>
@@ -11658,7 +11661,7 @@
       </c>
     </row>
     <row r="150" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A150" s="89"/>
+      <c r="A150" s="91"/>
       <c r="B150" s="46" t="s">
         <v>15</v>
       </c>
@@ -11724,7 +11727,7 @@
       </c>
     </row>
     <row r="151" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A151" s="87">
+      <c r="A151" s="89">
         <v>2014</v>
       </c>
       <c r="B151" s="16" t="s">
@@ -11792,7 +11795,7 @@
       </c>
     </row>
     <row r="152" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A152" s="88"/>
+      <c r="A152" s="90"/>
       <c r="B152" s="17" t="s">
         <v>17</v>
       </c>
@@ -11858,7 +11861,7 @@
       </c>
     </row>
     <row r="153" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A153" s="88"/>
+      <c r="A153" s="90"/>
       <c r="B153" s="43" t="s">
         <v>18</v>
       </c>
@@ -11924,7 +11927,7 @@
       </c>
     </row>
     <row r="154" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A154" s="88"/>
+      <c r="A154" s="90"/>
       <c r="B154" s="43" t="s">
         <v>19</v>
       </c>
@@ -11990,7 +11993,7 @@
       </c>
     </row>
     <row r="155" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="88"/>
+      <c r="A155" s="90"/>
       <c r="B155" s="43" t="s">
         <v>20</v>
       </c>
@@ -12056,7 +12059,7 @@
       </c>
     </row>
     <row r="156" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A156" s="88"/>
+      <c r="A156" s="90"/>
       <c r="B156" s="43" t="s">
         <v>21</v>
       </c>
@@ -12122,7 +12125,7 @@
       </c>
     </row>
     <row r="157" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="88"/>
+      <c r="A157" s="90"/>
       <c r="B157" s="17" t="s">
         <v>22</v>
       </c>
@@ -12188,7 +12191,7 @@
       </c>
     </row>
     <row r="158" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A158" s="88"/>
+      <c r="A158" s="90"/>
       <c r="B158" s="43" t="s">
         <v>23</v>
       </c>
@@ -12254,7 +12257,7 @@
       </c>
     </row>
     <row r="159" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="88"/>
+      <c r="A159" s="90"/>
       <c r="B159" s="43" t="s">
         <v>26</v>
       </c>
@@ -12320,7 +12323,7 @@
       </c>
     </row>
     <row r="160" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A160" s="88"/>
+      <c r="A160" s="90"/>
       <c r="B160" s="43" t="s">
         <v>13</v>
       </c>
@@ -12386,7 +12389,7 @@
       </c>
     </row>
     <row r="161" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A161" s="88"/>
+      <c r="A161" s="90"/>
       <c r="B161" s="43" t="s">
         <v>14</v>
       </c>
@@ -12452,7 +12455,7 @@
       </c>
     </row>
     <row r="162" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A162" s="89"/>
+      <c r="A162" s="91"/>
       <c r="B162" s="46" t="s">
         <v>15</v>
       </c>
@@ -12518,7 +12521,7 @@
       </c>
     </row>
     <row r="163" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A163" s="98">
+      <c r="A163" s="102">
         <v>2015</v>
       </c>
       <c r="B163" s="16" t="s">
@@ -12586,7 +12589,7 @@
       </c>
     </row>
     <row r="164" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A164" s="99"/>
+      <c r="A164" s="103"/>
       <c r="B164" s="17" t="s">
         <v>17</v>
       </c>
@@ -12652,7 +12655,7 @@
       </c>
     </row>
     <row r="165" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A165" s="99"/>
+      <c r="A165" s="103"/>
       <c r="B165" s="17" t="s">
         <v>18</v>
       </c>
@@ -12718,7 +12721,7 @@
       </c>
     </row>
     <row r="166" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A166" s="99"/>
+      <c r="A166" s="103"/>
       <c r="B166" s="17" t="s">
         <v>19</v>
       </c>
@@ -12784,7 +12787,7 @@
       </c>
     </row>
     <row r="167" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A167" s="99"/>
+      <c r="A167" s="103"/>
       <c r="B167" s="17" t="s">
         <v>20</v>
       </c>
@@ -12850,7 +12853,7 @@
       </c>
     </row>
     <row r="168" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A168" s="99"/>
+      <c r="A168" s="103"/>
       <c r="B168" s="17" t="s">
         <v>21</v>
       </c>
@@ -12916,7 +12919,7 @@
       </c>
     </row>
     <row r="169" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A169" s="99"/>
+      <c r="A169" s="103"/>
       <c r="B169" s="17" t="s">
         <v>22</v>
       </c>
@@ -12982,7 +12985,7 @@
       </c>
     </row>
     <row r="170" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A170" s="99"/>
+      <c r="A170" s="103"/>
       <c r="B170" s="17" t="s">
         <v>23</v>
       </c>
@@ -13048,7 +13051,7 @@
       </c>
     </row>
     <row r="171" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A171" s="99"/>
+      <c r="A171" s="103"/>
       <c r="B171" s="17" t="s">
         <v>26</v>
       </c>
@@ -13114,7 +13117,7 @@
       </c>
     </row>
     <row r="172" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A172" s="99"/>
+      <c r="A172" s="103"/>
       <c r="B172" s="17" t="s">
         <v>13</v>
       </c>
@@ -13180,7 +13183,7 @@
       </c>
     </row>
     <row r="173" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A173" s="99"/>
+      <c r="A173" s="103"/>
       <c r="B173" s="17" t="s">
         <v>14</v>
       </c>
@@ -13246,7 +13249,7 @@
       </c>
     </row>
     <row r="174" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A174" s="100"/>
+      <c r="A174" s="104"/>
       <c r="B174" s="18" t="s">
         <v>15</v>
       </c>
@@ -17282,7 +17285,7 @@
       </c>
     </row>
     <row r="235" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A235" s="96">
+      <c r="A235" s="85">
         <v>2021</v>
       </c>
       <c r="B235" s="16" t="s">
@@ -17350,7 +17353,7 @@
       </c>
     </row>
     <row r="236" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A236" s="85"/>
+      <c r="A236" s="86"/>
       <c r="B236" s="17" t="s">
         <v>17</v>
       </c>
@@ -17416,7 +17419,7 @@
       </c>
     </row>
     <row r="237" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A237" s="85"/>
+      <c r="A237" s="86"/>
       <c r="B237" s="17" t="s">
         <v>18</v>
       </c>
@@ -17482,7 +17485,7 @@
       </c>
     </row>
     <row r="238" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A238" s="85"/>
+      <c r="A238" s="86"/>
       <c r="B238" s="17" t="s">
         <v>19</v>
       </c>
@@ -17548,7 +17551,7 @@
       </c>
     </row>
     <row r="239" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A239" s="85"/>
+      <c r="A239" s="86"/>
       <c r="B239" s="17" t="s">
         <v>20</v>
       </c>
@@ -17614,7 +17617,7 @@
       </c>
     </row>
     <row r="240" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A240" s="85"/>
+      <c r="A240" s="86"/>
       <c r="B240" s="17" t="s">
         <v>21</v>
       </c>
@@ -17680,7 +17683,7 @@
       </c>
     </row>
     <row r="241" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A241" s="85"/>
+      <c r="A241" s="86"/>
       <c r="B241" s="17" t="s">
         <v>22</v>
       </c>
@@ -17746,7 +17749,7 @@
       </c>
     </row>
     <row r="242" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A242" s="85"/>
+      <c r="A242" s="86"/>
       <c r="B242" s="17" t="s">
         <v>23</v>
       </c>
@@ -17812,7 +17815,7 @@
       </c>
     </row>
     <row r="243" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A243" s="85"/>
+      <c r="A243" s="86"/>
       <c r="B243" s="17" t="s">
         <v>26</v>
       </c>
@@ -17878,7 +17881,7 @@
       </c>
     </row>
     <row r="244" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A244" s="85"/>
+      <c r="A244" s="86"/>
       <c r="B244" s="17" t="s">
         <v>13</v>
       </c>
@@ -17944,7 +17947,7 @@
       </c>
     </row>
     <row r="245" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A245" s="85"/>
+      <c r="A245" s="86"/>
       <c r="B245" s="17" t="s">
         <v>14</v>
       </c>
@@ -18010,7 +18013,7 @@
       </c>
     </row>
     <row r="246" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A246" s="97"/>
+      <c r="A246" s="88"/>
       <c r="B246" s="74" t="s">
         <v>15</v>
       </c>
@@ -18076,7 +18079,7 @@
       </c>
     </row>
     <row r="247" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A247" s="96">
+      <c r="A247" s="85">
         <v>2022</v>
       </c>
       <c r="B247" s="16" t="s">
@@ -18144,7 +18147,7 @@
       </c>
     </row>
     <row r="248" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A248" s="85"/>
+      <c r="A248" s="86"/>
       <c r="B248" s="17" t="s">
         <v>17</v>
       </c>
@@ -18210,7 +18213,7 @@
       </c>
     </row>
     <row r="249" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A249" s="85"/>
+      <c r="A249" s="86"/>
       <c r="B249" s="17" t="s">
         <v>18</v>
       </c>
@@ -18276,7 +18279,7 @@
       </c>
     </row>
     <row r="250" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A250" s="85"/>
+      <c r="A250" s="86"/>
       <c r="B250" s="17" t="s">
         <v>19</v>
       </c>
@@ -18342,7 +18345,7 @@
       </c>
     </row>
     <row r="251" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A251" s="85"/>
+      <c r="A251" s="86"/>
       <c r="B251" s="17" t="s">
         <v>20</v>
       </c>
@@ -18408,7 +18411,7 @@
       </c>
     </row>
     <row r="252" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A252" s="85"/>
+      <c r="A252" s="86"/>
       <c r="B252" s="43" t="s">
         <v>21</v>
       </c>
@@ -18474,7 +18477,7 @@
       </c>
     </row>
     <row r="253" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A253" s="85"/>
+      <c r="A253" s="86"/>
       <c r="B253" s="43" t="s">
         <v>22</v>
       </c>
@@ -18540,7 +18543,7 @@
       </c>
     </row>
     <row r="254" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A254" s="85"/>
+      <c r="A254" s="86"/>
       <c r="B254" s="43" t="s">
         <v>23</v>
       </c>
@@ -18606,7 +18609,7 @@
       </c>
     </row>
     <row r="255" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A255" s="85"/>
+      <c r="A255" s="86"/>
       <c r="B255" s="43" t="s">
         <v>26</v>
       </c>
@@ -18672,7 +18675,7 @@
       </c>
     </row>
     <row r="256" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A256" s="85"/>
+      <c r="A256" s="86"/>
       <c r="B256" s="43" t="s">
         <v>13</v>
       </c>
@@ -18738,7 +18741,7 @@
       </c>
     </row>
     <row r="257" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A257" s="85"/>
+      <c r="A257" s="86"/>
       <c r="B257" s="43" t="s">
         <v>14</v>
       </c>
@@ -18804,7 +18807,7 @@
       </c>
     </row>
     <row r="258" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A258" s="97"/>
+      <c r="A258" s="88"/>
       <c r="B258" s="79" t="s">
         <v>15</v>
       </c>
@@ -18870,7 +18873,7 @@
       </c>
     </row>
     <row r="259" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A259" s="96">
+      <c r="A259" s="85">
         <v>2023</v>
       </c>
       <c r="B259" s="16" t="s">
@@ -18938,7 +18941,7 @@
       </c>
     </row>
     <row r="260" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A260" s="85"/>
+      <c r="A260" s="86"/>
       <c r="B260" s="17" t="s">
         <v>17</v>
       </c>
@@ -19004,7 +19007,7 @@
       </c>
     </row>
     <row r="261" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A261" s="85"/>
+      <c r="A261" s="86"/>
       <c r="B261" s="17" t="s">
         <v>18</v>
       </c>
@@ -19070,7 +19073,7 @@
       </c>
     </row>
     <row r="262" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A262" s="85"/>
+      <c r="A262" s="86"/>
       <c r="B262" s="17" t="s">
         <v>19</v>
       </c>
@@ -19136,7 +19139,7 @@
       </c>
     </row>
     <row r="263" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A263" s="85"/>
+      <c r="A263" s="86"/>
       <c r="B263" s="17" t="s">
         <v>20</v>
       </c>
@@ -19202,7 +19205,7 @@
       </c>
     </row>
     <row r="264" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A264" s="85"/>
+      <c r="A264" s="86"/>
       <c r="B264" s="17" t="s">
         <v>21</v>
       </c>
@@ -19268,7 +19271,7 @@
       </c>
     </row>
     <row r="265" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A265" s="85"/>
+      <c r="A265" s="86"/>
       <c r="B265" s="17" t="s">
         <v>22</v>
       </c>
@@ -19334,7 +19337,7 @@
       </c>
     </row>
     <row r="266" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A266" s="85"/>
+      <c r="A266" s="86"/>
       <c r="B266" s="17" t="s">
         <v>23</v>
       </c>
@@ -19400,7 +19403,7 @@
       </c>
     </row>
     <row r="267" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A267" s="85"/>
+      <c r="A267" s="86"/>
       <c r="B267" s="17" t="s">
         <v>26</v>
       </c>
@@ -19466,7 +19469,7 @@
       </c>
     </row>
     <row r="268" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A268" s="85"/>
+      <c r="A268" s="86"/>
       <c r="B268" s="17" t="s">
         <v>13</v>
       </c>
@@ -19532,7 +19535,7 @@
       </c>
     </row>
     <row r="269" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A269" s="85"/>
+      <c r="A269" s="86"/>
       <c r="B269" s="17" t="s">
         <v>14</v>
       </c>
@@ -19598,7 +19601,7 @@
       </c>
     </row>
     <row r="270" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A270" s="97"/>
+      <c r="A270" s="88"/>
       <c r="B270" s="18" t="s">
         <v>15</v>
       </c>
@@ -19664,7 +19667,7 @@
       </c>
     </row>
     <row r="271" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A271" s="96">
+      <c r="A271" s="85">
         <v>2024</v>
       </c>
       <c r="B271" s="16" t="s">
@@ -19732,7 +19735,7 @@
       </c>
     </row>
     <row r="272" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A272" s="85"/>
+      <c r="A272" s="86"/>
       <c r="B272" s="17" t="s">
         <v>17</v>
       </c>
@@ -19798,7 +19801,7 @@
       </c>
     </row>
     <row r="273" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A273" s="85"/>
+      <c r="A273" s="86"/>
       <c r="B273" s="43" t="s">
         <v>18</v>
       </c>
@@ -19864,7 +19867,7 @@
       </c>
     </row>
     <row r="274" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A274" s="85"/>
+      <c r="A274" s="86"/>
       <c r="B274" s="17" t="s">
         <v>19</v>
       </c>
@@ -19930,7 +19933,7 @@
       </c>
     </row>
     <row r="275" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A275" s="85"/>
+      <c r="A275" s="86"/>
       <c r="B275" s="17" t="s">
         <v>20</v>
       </c>
@@ -19996,7 +19999,7 @@
       </c>
     </row>
     <row r="276" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A276" s="85"/>
+      <c r="A276" s="86"/>
       <c r="B276" s="17" t="s">
         <v>21</v>
       </c>
@@ -20062,7 +20065,7 @@
       </c>
     </row>
     <row r="277" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A277" s="85"/>
+      <c r="A277" s="86"/>
       <c r="B277" s="17" t="s">
         <v>22</v>
       </c>
@@ -20128,7 +20131,7 @@
       </c>
     </row>
     <row r="278" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A278" s="85"/>
+      <c r="A278" s="86"/>
       <c r="B278" s="17" t="s">
         <v>23</v>
       </c>
@@ -20194,7 +20197,7 @@
       </c>
     </row>
     <row r="279" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A279" s="85"/>
+      <c r="A279" s="86"/>
       <c r="B279" s="17" t="s">
         <v>26</v>
       </c>
@@ -20260,7 +20263,7 @@
       </c>
     </row>
     <row r="280" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A280" s="85"/>
+      <c r="A280" s="86"/>
       <c r="B280" s="17" t="s">
         <v>13</v>
       </c>
@@ -20326,7 +20329,7 @@
       </c>
     </row>
     <row r="281" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A281" s="85"/>
+      <c r="A281" s="86"/>
       <c r="B281" s="17" t="s">
         <v>14</v>
       </c>
@@ -20392,7 +20395,7 @@
       </c>
     </row>
     <row r="282" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A282" s="97"/>
+      <c r="A282" s="88"/>
       <c r="B282" s="18" t="s">
         <v>15</v>
       </c>
@@ -20526,7 +20529,7 @@
       </c>
     </row>
     <row r="284" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A284" s="85"/>
+      <c r="A284" s="86"/>
       <c r="B284" s="17" t="s">
         <v>17</v>
       </c>
@@ -20592,7 +20595,7 @@
       </c>
     </row>
     <row r="285" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A285" s="85"/>
+      <c r="A285" s="86"/>
       <c r="B285" s="43" t="s">
         <v>18</v>
       </c>
@@ -20658,7 +20661,7 @@
       </c>
     </row>
     <row r="286" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A286" s="85"/>
+      <c r="A286" s="86"/>
       <c r="B286" s="43" t="s">
         <v>19</v>
       </c>
@@ -20724,7 +20727,7 @@
       </c>
     </row>
     <row r="287" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A287" s="85"/>
+      <c r="A287" s="86"/>
       <c r="B287" s="43" t="s">
         <v>20</v>
       </c>
@@ -20790,7 +20793,7 @@
       </c>
     </row>
     <row r="288" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A288" s="85"/>
+      <c r="A288" s="86"/>
       <c r="B288" s="43" t="s">
         <v>21</v>
       </c>
@@ -20856,7 +20859,7 @@
       </c>
     </row>
     <row r="289" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A289" s="85"/>
+      <c r="A289" s="86"/>
       <c r="B289" s="43" t="s">
         <v>22</v>
       </c>
@@ -20922,7 +20925,7 @@
       </c>
     </row>
     <row r="290" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A290" s="85"/>
+      <c r="A290" s="86"/>
       <c r="B290" s="43" t="s">
         <v>23</v>
       </c>
@@ -20988,7 +20991,7 @@
       </c>
     </row>
     <row r="291" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A291" s="85"/>
+      <c r="A291" s="86"/>
       <c r="B291" s="43" t="s">
         <v>26</v>
       </c>
@@ -21054,7 +21057,7 @@
       </c>
     </row>
     <row r="292" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A292" s="85"/>
+      <c r="A292" s="86"/>
       <c r="B292" s="43" t="s">
         <v>13</v>
       </c>
@@ -21120,7 +21123,7 @@
       </c>
     </row>
     <row r="293" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A293" s="85"/>
+      <c r="A293" s="86"/>
       <c r="B293" s="43" t="s">
         <v>14</v>
       </c>
@@ -21185,145 +21188,276 @@
         <v>171.42306508171649</v>
       </c>
     </row>
-    <row r="294" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A294" s="86"/>
-      <c r="B294" s="84" t="s">
+    <row r="294" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A294" s="88"/>
+      <c r="B294" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="C294" s="80">
+      <c r="C294" s="54">
         <v>359552.85467389022</v>
       </c>
-      <c r="D294" s="81">
+      <c r="D294" s="30">
         <v>744093.14258765662</v>
       </c>
-      <c r="E294" s="81">
+      <c r="E294" s="30">
         <v>156568.77503007386</v>
       </c>
-      <c r="F294" s="81">
+      <c r="F294" s="30">
         <v>34637.260857281661</v>
       </c>
-      <c r="G294" s="81">
+      <c r="G294" s="30">
         <v>182200.1024579175</v>
       </c>
-      <c r="H294" s="81">
+      <c r="H294" s="30">
         <v>462692.56733868638</v>
       </c>
-      <c r="I294" s="81">
+      <c r="I294" s="30">
         <v>137095.8514124855</v>
       </c>
-      <c r="J294" s="81">
+      <c r="J294" s="30">
         <v>167568.66207185196</v>
       </c>
-      <c r="K294" s="81">
+      <c r="K294" s="30">
         <v>86056.768949800244</v>
       </c>
-      <c r="L294" s="82">
+      <c r="L294" s="31">
         <v>439680.28432392405</v>
       </c>
-      <c r="M294" s="80">
+      <c r="M294" s="54">
         <v>185.38509045112829</v>
       </c>
-      <c r="N294" s="81">
+      <c r="N294" s="30">
         <v>284.72929509103886</v>
       </c>
-      <c r="O294" s="81">
+      <c r="O294" s="30">
         <v>74.204128831382945</v>
       </c>
-      <c r="P294" s="81">
+      <c r="P294" s="30">
         <v>101.52774632408806</v>
       </c>
-      <c r="Q294" s="81">
+      <c r="Q294" s="30">
         <v>52.496465666161129</v>
       </c>
-      <c r="R294" s="81">
+      <c r="R294" s="30">
         <v>470.69280641824844</v>
       </c>
-      <c r="S294" s="81">
+      <c r="S294" s="30">
         <v>91.850379827949709</v>
       </c>
-      <c r="T294" s="81">
+      <c r="T294" s="30">
         <v>88.251614449483725</v>
       </c>
-      <c r="U294" s="81">
+      <c r="U294" s="30">
         <v>107.51787784078159</v>
       </c>
-      <c r="V294" s="82">
+      <c r="V294" s="31">
         <v>152.86685917183632</v>
       </c>
     </row>
     <row r="295" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A295" s="13" t="s">
+      <c r="A295" s="85" t="s">
+        <v>62</v>
+      </c>
+      <c r="B295" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C295" s="49">
+        <v>256722.62387808735</v>
+      </c>
+      <c r="D295" s="21">
+        <v>405308.81346038129</v>
+      </c>
+      <c r="E295" s="21">
+        <v>130850.23155350606</v>
+      </c>
+      <c r="F295" s="21">
+        <v>46716.748425766622</v>
+      </c>
+      <c r="G295" s="21">
+        <v>122982.15582405355</v>
+      </c>
+      <c r="H295" s="21">
+        <v>392951.99628987483</v>
+      </c>
+      <c r="I295" s="21">
+        <v>150676.44167118563</v>
+      </c>
+      <c r="J295" s="21">
+        <v>95184.583426433659</v>
+      </c>
+      <c r="K295" s="21">
+        <v>88597.43788119714</v>
+      </c>
+      <c r="L295" s="22">
+        <v>392150.11447644129</v>
+      </c>
+      <c r="M295" s="49">
+        <v>159.82204825207302</v>
+      </c>
+      <c r="N295" s="21">
+        <v>118.51372890233492</v>
+      </c>
+      <c r="O295" s="21">
+        <v>80.864906298775637</v>
+      </c>
+      <c r="P295" s="21">
+        <v>168.79455968546824</v>
+      </c>
+      <c r="Q295" s="21">
+        <v>93.137776845374916</v>
+      </c>
+      <c r="R295" s="21">
+        <v>389.15993343765717</v>
+      </c>
+      <c r="S295" s="21">
+        <v>106.19582542875634</v>
+      </c>
+      <c r="T295" s="21">
+        <v>79.111111500819391</v>
+      </c>
+      <c r="U295" s="21">
+        <v>152.5014822962269</v>
+      </c>
+      <c r="V295" s="22">
+        <v>148.49278520102155</v>
+      </c>
+    </row>
+    <row r="296" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A296" s="86"/>
+      <c r="B296" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C296" s="49">
+        <v>253585.22672625835</v>
+      </c>
+      <c r="D296" s="21">
+        <v>397101.77942081651</v>
+      </c>
+      <c r="E296" s="21">
+        <v>155432.8898560844</v>
+      </c>
+      <c r="F296" s="21">
+        <v>26263.282444160886</v>
+      </c>
+      <c r="G296" s="21">
+        <v>147849.97135288169</v>
+      </c>
+      <c r="H296" s="21">
+        <v>365158.11912187288</v>
+      </c>
+      <c r="I296" s="21">
+        <v>148686.97295942885</v>
+      </c>
+      <c r="J296" s="21">
+        <v>101240.82897777201</v>
+      </c>
+      <c r="K296" s="21">
+        <v>85997.078489456908</v>
+      </c>
+      <c r="L296" s="22">
+        <v>358247.18384872534</v>
+      </c>
+      <c r="M296" s="49">
+        <v>151.48004139379842</v>
+      </c>
+      <c r="N296" s="21">
+        <v>154.77428598555633</v>
+      </c>
+      <c r="O296" s="21">
+        <v>86.336493119034003</v>
+      </c>
+      <c r="P296" s="21">
+        <v>52.394692990871597</v>
+      </c>
+      <c r="Q296" s="21">
+        <v>91.269076958407737</v>
+      </c>
+      <c r="R296" s="21">
+        <v>331.88374241882104</v>
+      </c>
+      <c r="S296" s="21">
+        <v>108.31703148299475</v>
+      </c>
+      <c r="T296" s="21">
+        <v>85.920962975976096</v>
+      </c>
+      <c r="U296" s="21">
+        <v>118.49061262613284</v>
+      </c>
+      <c r="V296" s="22">
+        <v>125.09382606881042</v>
+      </c>
+    </row>
+    <row r="297" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A297" s="87"/>
+      <c r="B297" s="84" t="s">
+        <v>18</v>
+      </c>
+      <c r="C297" s="80">
+        <v>251978.57177243874</v>
+      </c>
+      <c r="D297" s="81">
+        <v>444885.52470570581</v>
+      </c>
+      <c r="E297" s="81">
+        <v>177015.91697160891</v>
+      </c>
+      <c r="F297" s="81">
+        <v>36549.671021279159</v>
+      </c>
+      <c r="G297" s="81">
+        <v>162941.12280194095</v>
+      </c>
+      <c r="H297" s="81">
+        <v>271746.7448521434</v>
+      </c>
+      <c r="I297" s="81">
+        <v>165093.82100197411</v>
+      </c>
+      <c r="J297" s="81">
+        <v>135291.04542362181</v>
+      </c>
+      <c r="K297" s="81">
+        <v>137109.43372061962</v>
+      </c>
+      <c r="L297" s="82">
+        <v>225536.5068935263</v>
+      </c>
+      <c r="M297" s="80">
+        <v>164.87226453514404</v>
+      </c>
+      <c r="N297" s="81">
+        <v>173.4971116169072</v>
+      </c>
+      <c r="O297" s="81">
+        <v>88.00599169849977</v>
+      </c>
+      <c r="P297" s="81">
+        <v>103.07220676213686</v>
+      </c>
+      <c r="Q297" s="81">
+        <v>94.242241214447574</v>
+      </c>
+      <c r="R297" s="81">
+        <v>286.66733710676772</v>
+      </c>
+      <c r="S297" s="81">
+        <v>112.99603698848317</v>
+      </c>
+      <c r="T297" s="81">
+        <v>120.29812019497344</v>
+      </c>
+      <c r="U297" s="81">
+        <v>231.4323227479116</v>
+      </c>
+      <c r="V297" s="82">
+        <v>81.259197969232545</v>
+      </c>
+    </row>
+    <row r="298" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A298" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C295" s="2"/>
-      <c r="D295" s="1"/>
-      <c r="E295" s="1"/>
-      <c r="F295" s="1"/>
-      <c r="G295" s="1"/>
-      <c r="H295" s="2"/>
-      <c r="I295" s="2"/>
-      <c r="J295" s="2"/>
-      <c r="K295" s="2"/>
-      <c r="L295" s="2"/>
-      <c r="M295" s="83"/>
-      <c r="N295" s="45"/>
-      <c r="O295" s="45"/>
-      <c r="P295" s="45"/>
-      <c r="Q295" s="45"/>
-      <c r="R295" s="45"/>
-      <c r="S295" s="45"/>
-      <c r="T295" s="45"/>
-      <c r="U295" s="45"/>
-      <c r="V295" s="45"/>
-    </row>
-    <row r="296" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A296" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="C296" s="2"/>
-      <c r="D296" s="1"/>
-      <c r="E296" s="1"/>
-      <c r="F296" s="1"/>
-      <c r="G296" s="1"/>
-      <c r="H296" s="2"/>
-      <c r="I296" s="2"/>
-      <c r="J296" s="2"/>
-      <c r="K296" s="2"/>
-      <c r="L296" s="2"/>
-      <c r="M296" s="2"/>
-      <c r="N296" s="2"/>
-      <c r="O296" s="1"/>
-      <c r="P296" s="1"/>
-      <c r="Q296" s="1"/>
-      <c r="R296" s="1"/>
-      <c r="S296" s="2"/>
-      <c r="T296" s="2"/>
-      <c r="U296" s="2"/>
-      <c r="V296" s="2"/>
-    </row>
-    <row r="297" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="C297" s="2"/>
-      <c r="D297" s="1"/>
-      <c r="E297" s="1"/>
-      <c r="F297" s="1"/>
-      <c r="G297" s="1"/>
-      <c r="H297" s="2"/>
-      <c r="I297" s="2"/>
-      <c r="J297" s="2"/>
-      <c r="K297" s="2"/>
-      <c r="L297" s="2"/>
-      <c r="M297" s="2"/>
-      <c r="N297" s="2"/>
-      <c r="O297" s="1"/>
-      <c r="P297" s="1"/>
-      <c r="Q297" s="1"/>
-      <c r="R297" s="1"/>
-      <c r="S297" s="2"/>
-      <c r="T297" s="2"/>
-      <c r="U297" s="2"/>
-      <c r="V297" s="2"/>
-    </row>
-    <row r="298" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C298" s="2"/>
       <c r="D298" s="1"/>
       <c r="E298" s="1"/>
@@ -21334,18 +21468,21 @@
       <c r="J298" s="2"/>
       <c r="K298" s="2"/>
       <c r="L298" s="2"/>
-      <c r="M298" s="2"/>
-      <c r="N298" s="2"/>
-      <c r="O298" s="1"/>
-      <c r="P298" s="1"/>
-      <c r="Q298" s="1"/>
-      <c r="R298" s="1"/>
-      <c r="S298" s="2"/>
-      <c r="T298" s="2"/>
-      <c r="U298" s="2"/>
-      <c r="V298" s="2"/>
+      <c r="M298" s="83"/>
+      <c r="N298" s="45"/>
+      <c r="O298" s="45"/>
+      <c r="P298" s="45"/>
+      <c r="Q298" s="45"/>
+      <c r="R298" s="45"/>
+      <c r="S298" s="45"/>
+      <c r="T298" s="45"/>
+      <c r="U298" s="45"/>
+      <c r="V298" s="45"/>
     </row>
     <row r="299" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A299" s="14" t="s">
+        <v>58</v>
+      </c>
       <c r="C299" s="2"/>
       <c r="D299" s="1"/>
       <c r="E299" s="1"/>
@@ -21610,34 +21747,70 @@
       <c r="V310" s="2"/>
     </row>
     <row r="311" spans="3:22" x14ac:dyDescent="0.2">
-      <c r="D311" s="8"/>
-      <c r="E311" s="8"/>
-      <c r="F311" s="8"/>
-      <c r="G311" s="8"/>
-      <c r="O311" s="3"/>
-      <c r="P311" s="3"/>
-      <c r="Q311" s="3"/>
-      <c r="R311" s="3"/>
+      <c r="C311" s="2"/>
+      <c r="D311" s="1"/>
+      <c r="E311" s="1"/>
+      <c r="F311" s="1"/>
+      <c r="G311" s="1"/>
+      <c r="H311" s="2"/>
+      <c r="I311" s="2"/>
+      <c r="J311" s="2"/>
+      <c r="K311" s="2"/>
+      <c r="L311" s="2"/>
+      <c r="M311" s="2"/>
+      <c r="N311" s="2"/>
+      <c r="O311" s="1"/>
+      <c r="P311" s="1"/>
+      <c r="Q311" s="1"/>
+      <c r="R311" s="1"/>
+      <c r="S311" s="2"/>
+      <c r="T311" s="2"/>
+      <c r="U311" s="2"/>
+      <c r="V311" s="2"/>
     </row>
     <row r="312" spans="3:22" x14ac:dyDescent="0.2">
-      <c r="D312" s="8"/>
-      <c r="E312" s="8"/>
-      <c r="F312" s="8"/>
-      <c r="G312" s="8"/>
-      <c r="O312" s="3"/>
-      <c r="P312" s="3"/>
-      <c r="Q312" s="3"/>
-      <c r="R312" s="3"/>
+      <c r="C312" s="2"/>
+      <c r="D312" s="1"/>
+      <c r="E312" s="1"/>
+      <c r="F312" s="1"/>
+      <c r="G312" s="1"/>
+      <c r="H312" s="2"/>
+      <c r="I312" s="2"/>
+      <c r="J312" s="2"/>
+      <c r="K312" s="2"/>
+      <c r="L312" s="2"/>
+      <c r="M312" s="2"/>
+      <c r="N312" s="2"/>
+      <c r="O312" s="1"/>
+      <c r="P312" s="1"/>
+      <c r="Q312" s="1"/>
+      <c r="R312" s="1"/>
+      <c r="S312" s="2"/>
+      <c r="T312" s="2"/>
+      <c r="U312" s="2"/>
+      <c r="V312" s="2"/>
     </row>
     <row r="313" spans="3:22" x14ac:dyDescent="0.2">
-      <c r="D313" s="8"/>
-      <c r="E313" s="8"/>
-      <c r="F313" s="8"/>
-      <c r="G313" s="8"/>
-      <c r="O313" s="3"/>
-      <c r="P313" s="3"/>
-      <c r="Q313" s="3"/>
-      <c r="R313" s="3"/>
+      <c r="C313" s="2"/>
+      <c r="D313" s="1"/>
+      <c r="E313" s="1"/>
+      <c r="F313" s="1"/>
+      <c r="G313" s="1"/>
+      <c r="H313" s="2"/>
+      <c r="I313" s="2"/>
+      <c r="J313" s="2"/>
+      <c r="K313" s="2"/>
+      <c r="L313" s="2"/>
+      <c r="M313" s="2"/>
+      <c r="N313" s="2"/>
+      <c r="O313" s="1"/>
+      <c r="P313" s="1"/>
+      <c r="Q313" s="1"/>
+      <c r="R313" s="1"/>
+      <c r="S313" s="2"/>
+      <c r="T313" s="2"/>
+      <c r="U313" s="2"/>
+      <c r="V313" s="2"/>
     </row>
     <row r="314" spans="3:22" x14ac:dyDescent="0.2">
       <c r="D314" s="8"/>
@@ -23229,8 +23402,50 @@
       <c r="Q472" s="3"/>
       <c r="R472" s="3"/>
     </row>
+    <row r="473" spans="4:18" x14ac:dyDescent="0.2">
+      <c r="D473" s="8"/>
+      <c r="E473" s="8"/>
+      <c r="F473" s="8"/>
+      <c r="G473" s="8"/>
+      <c r="O473" s="3"/>
+      <c r="P473" s="3"/>
+      <c r="Q473" s="3"/>
+      <c r="R473" s="3"/>
+    </row>
+    <row r="474" spans="4:18" x14ac:dyDescent="0.2">
+      <c r="D474" s="8"/>
+      <c r="E474" s="8"/>
+      <c r="F474" s="8"/>
+      <c r="G474" s="8"/>
+      <c r="O474" s="3"/>
+      <c r="P474" s="3"/>
+      <c r="Q474" s="3"/>
+      <c r="R474" s="3"/>
+    </row>
+    <row r="475" spans="4:18" x14ac:dyDescent="0.2">
+      <c r="D475" s="8"/>
+      <c r="E475" s="8"/>
+      <c r="F475" s="8"/>
+      <c r="G475" s="8"/>
+      <c r="O475" s="3"/>
+      <c r="P475" s="3"/>
+      <c r="Q475" s="3"/>
+      <c r="R475" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="26">
+    <mergeCell ref="A235:A246"/>
+    <mergeCell ref="A163:A174"/>
+    <mergeCell ref="A151:A162"/>
+    <mergeCell ref="M2:V2"/>
+    <mergeCell ref="A7:A18"/>
+    <mergeCell ref="A19:A30"/>
+    <mergeCell ref="A31:A42"/>
+    <mergeCell ref="A43:A54"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A295:A297"/>
+    <mergeCell ref="A283:A294"/>
     <mergeCell ref="A103:A114"/>
     <mergeCell ref="A115:A126"/>
     <mergeCell ref="A1:L1"/>
@@ -23240,22 +23455,11 @@
     <mergeCell ref="A67:A78"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="C2:L2"/>
-    <mergeCell ref="A283:A294"/>
     <mergeCell ref="A127:A138"/>
-    <mergeCell ref="M2:V2"/>
-    <mergeCell ref="A7:A18"/>
-    <mergeCell ref="A19:A30"/>
-    <mergeCell ref="A31:A42"/>
-    <mergeCell ref="A43:A54"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
     <mergeCell ref="A271:A282"/>
     <mergeCell ref="A139:A150"/>
     <mergeCell ref="A259:A270"/>
     <mergeCell ref="A247:A258"/>
-    <mergeCell ref="A235:A246"/>
-    <mergeCell ref="A163:A174"/>
-    <mergeCell ref="A151:A162"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
